--- a/exports/MAXKY_SALES.xlsx
+++ b/exports/MAXKY_SALES.xlsx
@@ -38,7 +38,7 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -495,6 +495,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -518,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>211</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -531,7 +532,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>297</v>
+        <v>21920.98</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -546,7 +547,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>170</v>
+        <v>12660</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -559,7 +560,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>127</v>
+        <v>9260.98</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -567,147 +568,7701 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>💵 เงินสด</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>17495</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>บาท</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>📱 โอนเงิน</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>3917.98</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>บาท</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>🤝 คนละครึ่ง</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>508</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>บาท</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>รายละเอียดการขาย</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>วันที่</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>ชื่องาน</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>สินค้า</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>ไซส์</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>ต้นทุน</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>ราคาขาย</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>กำไร</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-22 20:38:01</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>งานพระบาท</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>เสื้อกีฬา</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-22 20:38:01</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>งานพระบาท</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>เสื้อกีฬา</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>44</v>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>ช่องทางชำระ</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-22 20:38:01</t>
+          <t>2026-10-23 12:56:06</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>งานพระบาท</t>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:37:50</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E13" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:37:49</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:36:31</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G12" s="10" t="n">
+      <c r="F15" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G15" s="10" t="n">
         <v>44</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:36:30</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:36:28</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:36:26</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:34:18</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:34:16</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:34:14</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:32:15</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:32:13</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:18:37</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:14:37</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:06:56</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:06:55</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:01:16</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:01:15</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:01:13</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:55:01</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:54:41</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:54:26</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:54:24</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:54:23</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:18:39</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:54:31</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:53:48</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:48:28</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:48:27</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:48:25</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:42:29</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:42:15</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:38:50</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:38:49</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:38:47</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:38:46</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:38:44</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:31:15</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:20:19</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:07:43</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:07:42</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:50:51</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:50:49</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:50:47</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:31:27</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:31:23</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 07:41:41</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 07:41:40</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F59" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:41:44</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:30:39</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:19:16</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 05:19:15</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:41:25</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:41:24</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:24:21</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 03:02:01</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 03:02:00</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:36:34</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:42:05</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:42:04</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:41:30</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:11:48</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:11:47</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:10:30</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:53:02</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:48</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:46</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:45</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:38</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:37</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:44:35</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:36:21</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:36:19</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:22:36</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:12:21</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:12:00</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F87" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>คนละครึ่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:06:29</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:38:17</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F89" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:17:41</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:17:39</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:17:38</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:17:36</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F93" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:02:18</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:02:01</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F95" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G95" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:02:00</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:01:58</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:38:21</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:38:19</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F99" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G99" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:38:18</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:10:19</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G101" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:33:58</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:33:57</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F103" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:33:55</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:20:38</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F105" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:42:30</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:42:28</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G107" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:35:08</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:35:07</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F109" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:22:51</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:13:38</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F111" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G111" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>คนละครึ่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:04:15</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:04:13</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F113" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:11:41</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:11:40</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="F115" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G115" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:05:31</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:05:30</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F117" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G117" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:28</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:26</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F119" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:24</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:23</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F121" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G121" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:21</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:58:20</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F123" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G123" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:43:08</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:14:27</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G125" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 03:14:26</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:59:11</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F127" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G127" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:57:03</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:09:58</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F129" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G129" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:09:57</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:43:21</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F131" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G131" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:43:20</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:43:18</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F133" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G133" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:43:17</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:42:38</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F135" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:42:22</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:33:00</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G137" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:32:58</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G138" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:42:35</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อฟอก</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="F139" s="10" t="n">
+        <v>153.33</v>
+      </c>
+      <c r="G139" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:42:34</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="G140" s="10" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:42:32</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F141" s="10" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:40:53</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G142" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:40:51</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F143" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G143" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:12:24</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G144" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:04:00</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F145" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G145" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:28:53</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G146" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:28:51</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F147" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G147" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:28:25</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G148" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:18:07</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F149" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G149" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:03:38</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G150" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:42:43</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F151" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G151" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:06:13</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G152" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:21</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F153" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:20</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G154" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:18</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F155" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G155" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:17</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G156" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:15</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F157" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G157" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:58:14</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G158" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:12:11</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F159" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G159" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:12:09</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G160" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 05:05:15</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F161" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G161" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:29:02</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G162" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:02:39</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F163" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G163" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:55:22</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F164" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G164" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:55:20</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F165" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G165" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:26:16</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F166" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G166" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:11:00</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F167" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G167" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:10:58</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F168" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G168" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:47:43</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F169" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G169" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:42:10</t>
+        </is>
+      </c>
+      <c r="B170" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F170" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G170" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:42:08</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F171" s="10" t="n">
+        <v>159</v>
+      </c>
+      <c r="G171" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:27:32</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F172" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G172" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:27:30</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F173" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G173" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:27:29</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F174" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:15:35</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F175" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G175" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:03:38</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F176" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G176" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:06:30</t>
+        </is>
+      </c>
+      <c r="B177" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C177" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F177" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G177" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:06:28</t>
+        </is>
+      </c>
+      <c r="B178" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C178" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F178" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G178" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:53:57</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C179" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F179" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G179" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:18:17</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C180" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬาแขนยาว</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F180" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G180" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>คนละครึ่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:18:15</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืดแขนยาว</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F181" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G181" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>คนละครึ่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:54:57</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F182" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G182" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:54:56</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F183" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G183" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:33:40</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F184" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G184" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:15:31</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C185" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F185" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G185" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:15:29</t>
+        </is>
+      </c>
+      <c r="B186" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C186" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F186" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G186" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:08:11</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C187" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F187" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G187" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 09:29:03</t>
+        </is>
+      </c>
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F188" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G188" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:24:03</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C189" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F189" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G189" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:24:02</t>
+        </is>
+      </c>
+      <c r="B190" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C190" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F190" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G190" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:15:42</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C191" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F191" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G191" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H191" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:33:33</t>
+        </is>
+      </c>
+      <c r="B192" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F192" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G192" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H192" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:33:31</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F193" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G193" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H193" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:33:29</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F194" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G194" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H194" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 07:33:28</t>
+        </is>
+      </c>
+      <c r="B195" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H195" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01:14</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F196" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G196" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H196" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:59:54</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F197" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G197" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H197" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:59:52</t>
+        </is>
+      </c>
+      <c r="B198" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F198" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G198" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H198" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:43:03</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F199" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G199" s="10" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="H199" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:43:02</t>
+        </is>
+      </c>
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F200" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G200" s="10" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="H200" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:43:00</t>
+        </is>
+      </c>
+      <c r="B201" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E201" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F201" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G201" s="10" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="H201" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:42:58</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E202" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F202" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G202" s="10" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="H202" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:42:57</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E203" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F203" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G203" s="10" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="H203" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:42:55</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E204" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F204" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G204" s="10" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="H204" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:42:54</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C205" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E205" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F205" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G205" s="10" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="H205" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:42:52</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C206" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E206" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F206" s="10" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="G206" s="10" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="H206" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:20:48</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C207" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E207" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F207" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G207" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H207" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 05:01:04</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E208" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F208" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G208" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H208" s="9" t="inlineStr">
+        <is>
+          <t>โอนเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:20:18</t>
+        </is>
+      </c>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E209" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F209" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G209" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H209" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:20:17</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E210" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F210" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G210" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-20 03:58:57</t>
+        </is>
+      </c>
+      <c r="B211" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E211" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F211" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G211" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H211" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:19:42</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E212" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F212" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G212" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H212" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:19:40</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C213" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E213" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F213" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G213" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:19:39</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อยืด</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E214" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F214" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G214" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:13:46</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>กางเกง FT</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E215" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F215" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G215" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:13:45</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E216" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F216" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G216" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:13:44</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E217" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F217" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G217" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:16:37</t>
+        </is>
+      </c>
+      <c r="B218" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E218" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F218" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G218" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H218" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:14:20</t>
+        </is>
+      </c>
+      <c r="B219" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E219" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F219" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G219" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H219" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:28</t>
+        </is>
+      </c>
+      <c r="B220" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E220" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F220" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G220" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:26</t>
+        </is>
+      </c>
+      <c r="B221" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E221" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F221" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G221" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H221" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:24</t>
+        </is>
+      </c>
+      <c r="B222" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C222" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E222" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F222" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G222" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/MAXKY_SALES.xlsx
+++ b/exports/MAXKY_SALES.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>21920.98</v>
+        <v>22514.98</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>12660</v>
+        <v>13010</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>9260.98</v>
+        <v>9504.98</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>17495</v>
+        <v>18089</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:56:06</t>
+          <t>2026-10-23 13:19:43</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:37:50</t>
+          <t>2026-10-23 13:19:41</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:37:49</t>
+          <t>2026-10-23 13:19:40</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -748,22 +748,22 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:31</t>
+          <t>2026-10-23 13:19:38</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -789,17 +789,17 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:30</t>
+          <t>2026-10-23 13:10:05</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -825,17 +825,17 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:28</t>
+          <t>2026-10-23 13:06:49</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -856,22 +856,22 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:26</t>
+          <t>2026-10-23 12:56:06</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:18</t>
+          <t>2026-10-23 12:37:50</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -937,24 +937,24 @@
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:16</t>
+          <t>2026-10-23 12:37:49</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -964,33 +964,33 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:14</t>
+          <t>2026-10-23 12:36:31</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E21" s="10" t="n">
@@ -1019,14 +1019,14 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:32:15</t>
+          <t>2026-10-23 12:36:30</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F22" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:32:13</t>
+          <t>2026-10-23 12:36:28</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1072,22 +1072,22 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F23" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:18:37</t>
+          <t>2026-10-23 12:36:26</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:14:37</t>
+          <t>2026-10-23 12:34:18</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:06:56</t>
+          <t>2026-10-23 12:34:16</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1199,14 +1199,14 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:06:55</t>
+          <t>2026-10-23 12:34:14</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1235,14 +1235,14 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:16</t>
+          <t>2026-10-23 12:32:15</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E28" s="10" t="n">
@@ -1278,7 +1278,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:15</t>
+          <t>2026-10-23 12:32:13</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
@@ -1314,7 +1314,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:13</t>
+          <t>2026-10-23 12:18:37</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:55:01</t>
+          <t>2026-10-23 12:14:37</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1360,33 +1360,33 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:41</t>
+          <t>2026-10-23 12:06:56</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E32" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F32" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:26</t>
+          <t>2026-10-23 12:06:55</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E33" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F33" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:24</t>
+          <t>2026-10-23 12:01:16</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1468,22 +1468,22 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E34" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:23</t>
+          <t>2026-10-23 12:01:15</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:18:39</t>
+          <t>2026-10-23 12:01:13</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:54:31</t>
+          <t>2026-10-23 11:55:01</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1576,22 +1576,22 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E37" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:53:48</t>
+          <t>2026-10-23 11:54:41</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1612,22 +1612,22 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F38" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:28</t>
+          <t>2026-10-23 11:54:26</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E39" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>96.67</v>
+        <v>99</v>
       </c>
       <c r="G39" s="10" t="n">
-        <v>26.67</v>
+        <v>39</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:27</t>
+          <t>2026-10-23 11:54:24</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1684,22 +1684,22 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
         <v>70</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>96.67</v>
+        <v>120</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>26.67</v>
+        <v>50</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:25</t>
+          <t>2026-10-23 11:54:23</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>96.67</v>
+        <v>99</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>26.67</v>
+        <v>34</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:42:29</t>
+          <t>2026-10-23 11:18:39</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E42" s="10" t="n">
@@ -1782,7 +1782,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:42:15</t>
+          <t>2026-10-23 10:54:31</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1792,33 +1792,33 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E43" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:50</t>
+          <t>2026-10-23 10:53:48</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F44" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:49</t>
+          <t>2026-10-23 10:48:28</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -1864,22 +1864,22 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>99</v>
+        <v>96.67</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>44</v>
+        <v>26.67</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:47</t>
+          <t>2026-10-23 10:48:27</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -1900,22 +1900,22 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>99</v>
+        <v>96.67</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>44</v>
+        <v>26.67</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:46</t>
+          <t>2026-10-23 10:48:25</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -1936,22 +1936,22 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E47" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>99</v>
+        <v>96.67</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>44</v>
+        <v>26.67</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:44</t>
+          <t>2026-10-23 10:42:29</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:31:15</t>
+          <t>2026-10-23 10:42:15</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2017,24 +2017,24 @@
         </is>
       </c>
       <c r="E49" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:20:19</t>
+          <t>2026-10-23 10:38:50</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F50" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:07:43</t>
+          <t>2026-10-23 10:38:49</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -2080,22 +2080,22 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:07:42</t>
+          <t>2026-10-23 10:38:47</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E52" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:51</t>
+          <t>2026-10-23 10:38:46</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E53" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F53" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:49</t>
+          <t>2026-10-23 10:38:44</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -2188,22 +2188,22 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E54" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F54" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:47</t>
+          <t>2026-10-23 10:31:15</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2224,22 +2224,22 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:31:27</t>
+          <t>2026-10-23 10:20:19</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -2269,13 +2269,13 @@
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F56" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:31:23</t>
+          <t>2026-10-23 09:07:43</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -2296,22 +2296,22 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 07:41:41</t>
+          <t>2026-10-23 09:07:42</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -2332,33 +2332,33 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 07:41:40</t>
+          <t>2026-10-23 08:50:51</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -2373,28 +2373,28 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F59" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 06:41:44</t>
+          <t>2026-10-23 08:50:49</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 06:30:39</t>
+          <t>2026-10-23 08:50:47</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -2445,17 +2445,17 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F61" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 05:19:16</t>
+          <t>2026-10-23 08:31:27</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="E62" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F62" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 05:19:15</t>
+          <t>2026-10-23 08:31:23</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:41:25</t>
+          <t>2026-10-23 07:41:41</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2557,24 +2557,24 @@
         </is>
       </c>
       <c r="E64" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F64" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:41:24</t>
+          <t>2026-10-23 07:41:40</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -2589,28 +2589,28 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E65" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F65" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:24:21</t>
+          <t>2026-10-23 06:41:44</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -2620,22 +2620,22 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:02:01</t>
+          <t>2026-10-23 06:30:39</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -2656,22 +2656,22 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E67" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:02:00</t>
+          <t>2026-10-23 05:19:16</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E68" s="10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F68" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 16:36:34</t>
+          <t>2026-10-23 05:19:15</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -2733,28 +2733,28 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:42:05</t>
+          <t>2026-10-23 04:41:25</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:42:04</t>
+          <t>2026-10-23 04:41:24</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:41:30</t>
+          <t>2026-10-23 04:24:21</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -2841,28 +2841,28 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E72" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F72" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:11:48</t>
+          <t>2026-10-23 03:02:01</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -2872,33 +2872,33 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E73" s="10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:11:47</t>
+          <t>2026-10-23 03:02:00</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -2908,33 +2908,33 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:10:30</t>
+          <t>2026-10-22 16:36:34</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E75" s="10" t="n">
@@ -2970,7 +2970,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:53:02</t>
+          <t>2026-10-22 14:42:05</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:48</t>
+          <t>2026-10-22 14:42:04</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -3016,33 +3016,33 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E77" s="10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>98.33</v>
+        <v>159</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>38.33</v>
+        <v>84</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:46</t>
+          <t>2026-10-22 14:41:30</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -3057,17 +3057,17 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E78" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>38.33</v>
+        <v>44</v>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:45</t>
+          <t>2026-10-22 14:11:48</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>98.33</v>
+        <v>120</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>38.33</v>
+        <v>20</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:38</t>
+          <t>2026-10-22 14:11:47</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -3124,22 +3124,22 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E80" s="10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>98.33</v>
+        <v>120</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>38.33</v>
+        <v>20</v>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:37</t>
+          <t>2026-10-22 14:10:30</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E81" s="10" t="n">
         <v>60</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>38.33</v>
+        <v>39</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:35</t>
+          <t>2026-10-22 13:53:02</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -3201,28 +3201,28 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E82" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>38.33</v>
+        <v>44</v>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:36:21</t>
+          <t>2026-10-22 13:44:48</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3232,33 +3232,33 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E83" s="10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>97</v>
+        <v>98.33</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>62</v>
+        <v>38.33</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:36:19</t>
+          <t>2026-10-22 13:44:46</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>97</v>
+        <v>98.33</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>42</v>
+        <v>38.33</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:22:36</t>
+          <t>2026-10-22 13:44:45</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3304,33 +3304,33 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E85" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>99</v>
+        <v>98.33</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>34</v>
+        <v>38.33</v>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:12:21</t>
+          <t>2026-10-22 13:44:38</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -3349,24 +3349,24 @@
         </is>
       </c>
       <c r="E86" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>99</v>
+        <v>98.33</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>49</v>
+        <v>38.33</v>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:12:00</t>
+          <t>2026-10-22 13:44:37</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3376,33 +3376,33 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E87" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>99</v>
+        <v>98.33</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>34</v>
+        <v>38.33</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:06:29</t>
+          <t>2026-10-22 13:44:35</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -3424,21 +3424,21 @@
         <v>60</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>99</v>
+        <v>98.33</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>39</v>
+        <v>38.33</v>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:38:17</t>
+          <t>2026-10-22 13:36:21</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -3448,22 +3448,22 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E89" s="10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:41</t>
+          <t>2026-10-22 13:36:19</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -3484,22 +3484,22 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E90" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:39</t>
+          <t>2026-10-22 13:22:36</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F91" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 13:12:21</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E92" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F92" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:36</t>
+          <t>2026-10-22 13:12:00</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -3597,28 +3597,28 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E93" s="10" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F93" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:18</t>
+          <t>2026-10-22 13:06:29</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -3633,17 +3633,17 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E94" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:01</t>
+          <t>2026-10-22 12:38:17</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -3664,22 +3664,22 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E95" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F95" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:00</t>
+          <t>2026-10-22 12:17:41</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -3726,7 +3726,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:58</t>
+          <t>2026-10-22 12:17:39</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:21</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -3798,7 +3798,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:19</t>
+          <t>2026-10-22 12:17:36</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E99" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:18</t>
+          <t>2026-10-22 12:02:18</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -3844,22 +3844,22 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E100" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:10:19</t>
+          <t>2026-10-22 12:02:01</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E101" s="10" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F101" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:58</t>
+          <t>2026-10-22 12:02:00</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E102" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F102" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:57</t>
+          <t>2026-10-22 12:01:58</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -3952,22 +3952,22 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E103" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F103" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:55</t>
+          <t>2026-10-22 11:38:21</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -3988,22 +3988,22 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E104" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:20:38</t>
+          <t>2026-10-22 11:38:19</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
@@ -4033,13 +4033,13 @@
         </is>
       </c>
       <c r="E105" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:42:30</t>
+          <t>2026-10-22 11:38:18</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:42:28</t>
+          <t>2026-10-22 11:10:19</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E107" s="10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G107" s="10" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:35:08</t>
+          <t>2026-10-22 10:33:58</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -4132,33 +4132,33 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E108" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:35:07</t>
+          <t>2026-10-22 10:33:57</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:51</t>
+          <t>2026-10-22 10:33:55</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E110" s="10" t="n">
@@ -4230,7 +4230,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:13:38</t>
+          <t>2026-10-22 10:20:38</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
@@ -4249,24 +4249,24 @@
         </is>
       </c>
       <c r="E111" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F111" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G111" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 07:04:15</t>
+          <t>2026-10-22 09:42:30</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
@@ -4285,13 +4285,13 @@
         </is>
       </c>
       <c r="E112" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F112" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 07:04:13</t>
+          <t>2026-10-22 09:42:28</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
@@ -4321,13 +4321,13 @@
         </is>
       </c>
       <c r="E113" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F113" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:11:41</t>
+          <t>2026-10-22 09:35:08</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -4353,28 +4353,28 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E114" s="10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:11:40</t>
+          <t>2026-10-22 09:35:07</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -4384,33 +4384,33 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E115" s="10" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F115" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:05:31</t>
+          <t>2026-10-22 09:22:51</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
@@ -4429,24 +4429,24 @@
         </is>
       </c>
       <c r="E116" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F116" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:05:30</t>
+          <t>2026-10-22 09:13:38</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
@@ -4465,24 +4465,24 @@
         </is>
       </c>
       <c r="E117" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F117" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:28</t>
+          <t>2026-10-22 07:04:15</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E118" s="10" t="n">
@@ -4518,7 +4518,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:26</t>
+          <t>2026-10-22 07:04:13</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -4537,13 +4537,13 @@
         </is>
       </c>
       <c r="E119" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F119" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:24</t>
+          <t>2026-10-22 06:11:41</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
@@ -4573,13 +4573,13 @@
         </is>
       </c>
       <c r="E120" s="10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G120" s="10" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:23</t>
+          <t>2026-10-22 06:11:40</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -4600,22 +4600,22 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E121" s="10" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:21</t>
+          <t>2026-10-22 06:05:31</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E122" s="10" t="n">
@@ -4655,14 +4655,14 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:20</t>
+          <t>2026-10-22 06:05:30</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E123" s="10" t="n">
@@ -4691,14 +4691,14 @@
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:43:08</t>
+          <t>2026-10-22 03:58:28</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -4713,17 +4713,17 @@
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E124" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F124" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G124" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:14:27</t>
+          <t>2026-10-22 03:58:26</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
@@ -4753,13 +4753,13 @@
         </is>
       </c>
       <c r="E125" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F125" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:14:26</t>
+          <t>2026-10-22 03:58:24</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -4780,22 +4780,22 @@
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E126" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F126" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G126" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 02:59:11</t>
+          <t>2026-10-22 03:58:23</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E127" s="10" t="n">
@@ -4842,7 +4842,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:57:03</t>
+          <t>2026-10-22 03:58:21</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -4852,22 +4852,22 @@
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E128" s="10" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G128" s="10" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:09:58</t>
+          <t>2026-10-22 03:58:20</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E129" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F129" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G129" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:09:57</t>
+          <t>2026-10-22 03:43:08</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:21</t>
+          <t>2026-10-22 03:14:27</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E131" s="10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F131" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G131" s="10" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:20</t>
+          <t>2026-10-22 03:14:26</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E132" s="10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G132" s="10" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:18</t>
+          <t>2026-10-22 02:59:11</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:17</t>
+          <t>2026-10-21 14:57:03</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -5068,22 +5068,22 @@
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E134" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G134" s="10" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:38</t>
+          <t>2026-10-21 14:09:58</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E135" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F135" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G135" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:22</t>
+          <t>2026-10-21 14:09:57</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -5145,28 +5145,28 @@
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E136" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F136" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G136" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:33:00</t>
+          <t>2026-10-21 13:43:21</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -5181,17 +5181,17 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E137" s="10" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F137" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G137" s="10" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:32:58</t>
+          <t>2026-10-21 13:43:20</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -5212,22 +5212,22 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E138" s="10" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G138" s="10" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:35</t>
+          <t>2026-10-21 13:43:18</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -5248,22 +5248,22 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E139" s="10" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="F139" s="10" t="n">
-        <v>153.33</v>
+        <v>99</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>38.33</v>
+        <v>44</v>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:34</t>
+          <t>2026-10-21 13:43:17</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="E140" s="10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>93.33</v>
+        <v>99</v>
       </c>
       <c r="G140" s="10" t="n">
-        <v>58.33</v>
+        <v>44</v>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:32</t>
+          <t>2026-10-21 13:42:38</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -5332,10 +5332,10 @@
         <v>55</v>
       </c>
       <c r="F141" s="10" t="n">
-        <v>93.33</v>
+        <v>99</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>38.33</v>
+        <v>44</v>
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:40:53</t>
+          <t>2026-10-21 13:42:22</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -5356,33 +5356,33 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E142" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F142" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G142" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:40:51</t>
+          <t>2026-10-21 13:33:00</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E143" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F143" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:12:24</t>
+          <t>2026-10-21 13:32:58</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -5433,17 +5433,17 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E144" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F144" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G144" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:04:00</t>
+          <t>2026-10-21 12:42:35</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -5464,33 +5464,33 @@
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E145" s="10" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>99</v>
+        <v>153.33</v>
       </c>
       <c r="G145" s="10" t="n">
-        <v>39</v>
+        <v>38.33</v>
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:53</t>
+          <t>2026-10-21 12:42:34</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="E146" s="10" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>99</v>
+        <v>93.33</v>
       </c>
       <c r="G146" s="10" t="n">
-        <v>44</v>
+        <v>58.33</v>
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:51</t>
+          <t>2026-10-21 12:42:32</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
@@ -5548,10 +5548,10 @@
         <v>55</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>99</v>
+        <v>93.33</v>
       </c>
       <c r="G147" s="10" t="n">
-        <v>44</v>
+        <v>38.33</v>
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:25</t>
+          <t>2026-10-21 12:40:53</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -5572,33 +5572,33 @@
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E148" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G148" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:07</t>
+          <t>2026-10-21 12:40:51</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C149" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="E149" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F149" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G149" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:03:38</t>
+          <t>2026-10-21 11:12:24</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -5644,22 +5644,22 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E150" s="10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F150" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G150" s="10" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:42:43</t>
+          <t>2026-10-21 11:04:00</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E151" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F151" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G151" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 06:06:13</t>
+          <t>2026-10-21 10:28:53</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E152" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F152" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G152" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:21</t>
+          <t>2026-10-21 10:28:51</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E153" s="10" t="n">
@@ -5778,7 +5778,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:20</t>
+          <t>2026-10-21 10:28:25</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -5793,28 +5793,28 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E154" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F154" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G154" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:18</t>
+          <t>2026-10-21 10:18:07</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C155" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
@@ -5833,13 +5833,13 @@
         </is>
       </c>
       <c r="E155" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F155" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G155" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:17</t>
+          <t>2026-10-21 10:03:38</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -5860,22 +5860,22 @@
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E156" s="10" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F156" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G156" s="10" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:15</t>
+          <t>2026-10-21 08:42:43</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E157" s="10" t="n">
@@ -5915,14 +5915,14 @@
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:14</t>
+          <t>2026-10-21 06:06:13</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E158" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F158" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G158" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:12:11</t>
+          <t>2026-10-21 05:58:21</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -5973,17 +5973,17 @@
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E159" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F159" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G159" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:12:09</t>
+          <t>2026-10-21 05:58:20</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -6030,7 +6030,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:05:15</t>
+          <t>2026-10-21 05:58:18</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -6066,7 +6066,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 04:29:02</t>
+          <t>2026-10-21 05:58:17</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E162" s="10" t="n">
@@ -6102,7 +6102,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 04:02:39</t>
+          <t>2026-10-21 05:58:15</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -6117,17 +6117,17 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E163" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F163" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G163" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:55:22</t>
+          <t>2026-10-21 05:58:14</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:55:20</t>
+          <t>2026-10-21 05:12:11</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E165" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F165" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G165" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:26:16</t>
+          <t>2026-10-21 05:12:09</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E166" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F166" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G166" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:11:00</t>
+          <t>2026-10-21 05:05:15</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E167" s="10" t="n">
@@ -6282,7 +6282,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:10:58</t>
+          <t>2026-10-21 04:29:02</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:47:43</t>
+          <t>2026-10-21 04:02:39</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
@@ -6337,13 +6337,13 @@
         </is>
       </c>
       <c r="E169" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F169" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G169" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:42:10</t>
+          <t>2026-10-20 14:55:22</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -6364,22 +6364,22 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E170" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G170" s="10" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:42:08</t>
+          <t>2026-10-20 14:55:20</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -6400,22 +6400,22 @@
       </c>
       <c r="C171" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E171" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F171" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G171" s="10" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:32</t>
+          <t>2026-10-20 14:26:16</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E172" s="10" t="n">
@@ -6462,7 +6462,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:30</t>
+          <t>2026-10-20 14:11:00</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E173" s="10" t="n">
@@ -6498,7 +6498,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:29</t>
+          <t>2026-10-20 14:10:58</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:15:35</t>
+          <t>2026-10-20 13:47:43</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -6544,22 +6544,22 @@
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E175" s="10" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F175" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G175" s="10" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:03:38</t>
+          <t>2026-10-20 13:42:10</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E176" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G176" s="10" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 12:06:30</t>
+          <t>2026-10-20 13:42:08</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -6616,22 +6616,22 @@
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E177" s="10" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G177" s="10" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 12:06:28</t>
+          <t>2026-10-20 13:27:32</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -6652,22 +6652,22 @@
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E178" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F178" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G178" s="10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:53:57</t>
+          <t>2026-10-20 13:27:30</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="E179" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F179" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G179" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:18:17</t>
+          <t>2026-10-20 13:27:29</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -6724,33 +6724,33 @@
       </c>
       <c r="C180" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬาแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E180" s="10" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G180" s="10" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:18:15</t>
+          <t>2026-10-20 13:15:35</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -6760,33 +6760,33 @@
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E181" s="10" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="F181" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G181" s="10" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:54:57</t>
+          <t>2026-10-20 13:03:38</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -6822,7 +6822,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:54:56</t>
+          <t>2026-10-20 12:06:30</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -6832,22 +6832,22 @@
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E183" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F183" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G183" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33:40</t>
+          <t>2026-10-20 12:06:28</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E184" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F184" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G184" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:15:31</t>
+          <t>2026-10-20 11:53:57</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -6904,22 +6904,22 @@
       </c>
       <c r="C185" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E185" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F185" s="10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G185" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:15:29</t>
+          <t>2026-10-20 11:18:17</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬาแขนยาว</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E186" s="10" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="G186" s="10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:08:11</t>
+          <t>2026-10-20 11:18:15</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
@@ -6985,24 +6985,24 @@
         </is>
       </c>
       <c r="E187" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G187" s="10" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 09:29:03</t>
+          <t>2026-10-20 10:54:57</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -7012,22 +7012,22 @@
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E188" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F188" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G188" s="10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:24:03</t>
+          <t>2026-10-20 10:54:56</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E189" s="10" t="n">
@@ -7074,7 +7074,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:24:02</t>
+          <t>2026-10-20 10:33:40</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E190" s="10" t="n">
@@ -7110,7 +7110,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:15:42</t>
+          <t>2026-10-20 10:15:31</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -7120,22 +7120,22 @@
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E191" s="10" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G191" s="10" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:33</t>
+          <t>2026-10-20 10:15:29</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -7156,22 +7156,22 @@
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E192" s="10" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G192" s="10" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:31</t>
+          <t>2026-10-20 10:08:11</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E193" s="10" t="n">
@@ -7211,14 +7211,14 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:29</t>
+          <t>2026-10-20 09:29:03</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -7228,22 +7228,22 @@
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E194" s="10" t="n">
         <v>70</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G194" s="10" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:28</t>
+          <t>2026-10-20 08:24:03</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -7269,17 +7269,17 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E195" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F195" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G195" s="10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 06:01:14</t>
+          <t>2026-10-20 08:24:02</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
@@ -7309,13 +7309,13 @@
         </is>
       </c>
       <c r="E196" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F196" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G196" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:59:54</t>
+          <t>2026-10-20 08:15:42</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -7336,33 +7336,33 @@
       </c>
       <c r="C197" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E197" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F197" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G197" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:59:52</t>
+          <t>2026-10-20 07:33:33</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:03</t>
+          <t>2026-10-20 07:33:31</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -7408,33 +7408,33 @@
       </c>
       <c r="C199" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E199" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F199" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G199" s="10" t="n">
-        <v>48.75</v>
+        <v>39</v>
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:02</t>
+          <t>2026-10-20 07:33:29</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -7444,33 +7444,33 @@
       </c>
       <c r="C200" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E200" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F200" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G200" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="F200" s="10" t="n">
-        <v>98.75</v>
-      </c>
-      <c r="G200" s="10" t="n">
-        <v>48.75</v>
-      </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:00</t>
+          <t>2026-10-20 07:33:28</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -7480,33 +7480,33 @@
       </c>
       <c r="C201" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E201" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>98.75</v>
+        <v>120</v>
       </c>
       <c r="G201" s="10" t="n">
-        <v>38.75</v>
+        <v>50</v>
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:58</t>
+          <t>2026-10-20 06:01:14</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -7516,33 +7516,33 @@
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E202" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F202" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G202" s="10" t="n">
-        <v>43.75</v>
+        <v>49</v>
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:57</t>
+          <t>2026-10-20 05:59:54</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -7552,22 +7552,22 @@
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E203" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F203" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G203" s="10" t="n">
-        <v>43.75</v>
+        <v>49</v>
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:55</t>
+          <t>2026-10-20 05:59:52</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -7600,10 +7600,10 @@
         <v>60</v>
       </c>
       <c r="F204" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G204" s="10" t="n">
-        <v>38.75</v>
+        <v>39</v>
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:54</t>
+          <t>2026-10-20 05:43:03</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -7624,22 +7624,22 @@
       </c>
       <c r="C205" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E205" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F205" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G205" s="10" t="n">
-        <v>38.75</v>
+        <v>48.75</v>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:52</t>
+          <t>2026-10-20 05:43:02</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -7660,22 +7660,22 @@
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E206" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F206" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G206" s="10" t="n">
-        <v>38.75</v>
+        <v>48.75</v>
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:20:48</t>
+          <t>2026-10-20 05:43:00</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -7708,21 +7708,21 @@
         <v>60</v>
       </c>
       <c r="F207" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G207" s="10" t="n">
-        <v>39</v>
+        <v>38.75</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:01:04</t>
+          <t>2026-10-20 05:42:58</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -7744,10 +7744,10 @@
         <v>55</v>
       </c>
       <c r="F208" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G208" s="10" t="n">
-        <v>44</v>
+        <v>43.75</v>
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 04:20:18</t>
+          <t>2026-10-20 05:42:57</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -7768,33 +7768,33 @@
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E209" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F209" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G209" s="10" t="n">
-        <v>29</v>
+        <v>43.75</v>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 04:20:17</t>
+          <t>2026-10-20 05:42:55</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="C210" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
@@ -7813,24 +7813,24 @@
         </is>
       </c>
       <c r="E210" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F210" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G210" s="10" t="n">
-        <v>29</v>
+        <v>38.75</v>
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 03:58:57</t>
+          <t>2026-10-20 05:42:54</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -7852,21 +7852,21 @@
         <v>60</v>
       </c>
       <c r="F211" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G211" s="10" t="n">
-        <v>39</v>
+        <v>38.75</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:42</t>
+          <t>2026-10-20 05:42:52</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -7881,28 +7881,28 @@
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E212" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F212" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G212" s="10" t="n">
-        <v>44</v>
+        <v>38.75</v>
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:40</t>
+          <t>2026-10-20 05:20:48</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -7912,22 +7912,22 @@
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E213" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F213" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G213" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:39</t>
+          <t>2026-10-20 05:01:04</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C214" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:46</t>
+          <t>2026-10-20 04:20:18</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -7984,22 +7984,22 @@
       </c>
       <c r="C215" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E215" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F215" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G215" s="10" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:45</t>
+          <t>2026-10-20 04:20:17</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="E216" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F216" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G216" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:44</t>
+          <t>2026-10-20 03:58:57</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:16:37</t>
+          <t>2026-10-19 13:19:42</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -8118,7 +8118,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:14:20</t>
+          <t>2026-10-19 13:19:40</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -8133,17 +8133,17 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E219" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F219" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G219" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:28</t>
+          <t>2026-10-19 13:19:39</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -8164,22 +8164,22 @@
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E220" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F220" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G220" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H220" s="9" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:26</t>
+          <t>2026-10-19 13:13:46</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -8200,22 +8200,22 @@
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E221" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F221" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G221" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:24</t>
+          <t>2026-10-19 13:13:45</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E222" s="10" t="n">
@@ -8254,6 +8254,222 @@
         <v>39</v>
       </c>
       <c r="H222" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:13:44</t>
+        </is>
+      </c>
+      <c r="B223" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C223" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E223" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F223" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G223" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H223" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:16:37</t>
+        </is>
+      </c>
+      <c r="B224" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C224" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E224" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F224" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G224" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H224" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 11:14:20</t>
+        </is>
+      </c>
+      <c r="B225" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C225" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E225" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F225" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G225" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:28</t>
+        </is>
+      </c>
+      <c r="B226" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C226" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E226" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F226" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G226" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:26</t>
+        </is>
+      </c>
+      <c r="B227" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E227" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F227" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G227" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:24</t>
+        </is>
+      </c>
+      <c r="B228" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E228" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F228" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G228" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
         <is>
           <t>เงินสด</t>
         </is>

--- a/exports/MAXKY_SALES.xlsx
+++ b/exports/MAXKY_SALES.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H228"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>22514.98</v>
+        <v>22712.98</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>13010</v>
+        <v>13110</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>9504.98</v>
+        <v>9602.98</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>18089</v>
+        <v>18287</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:19:43</t>
+          <t>2026-10-23 13:36:14</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -676,22 +676,22 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:19:41</t>
+          <t>2026-10-23 13:36:13</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:19:40</t>
+          <t>2026-10-23 13:19:43</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E14" s="10" t="n">
@@ -774,7 +774,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:19:38</t>
+          <t>2026-10-23 13:19:41</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E15" s="10" t="n">
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:10:05</t>
+          <t>2026-10-23 13:19:40</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E16" s="10" t="n">
@@ -846,7 +846,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 13:06:49</t>
+          <t>2026-10-23 13:19:38</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="E17" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:56:06</t>
+          <t>2026-10-23 13:10:05</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="E18" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F18" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:37:50</t>
+          <t>2026-10-23 13:06:49</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E19" s="10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F19" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:37:49</t>
+          <t>2026-10-23 12:56:06</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -964,22 +964,22 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:31</t>
+          <t>2026-10-23 12:37:50</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1000,22 +1000,22 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E21" s="10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:30</t>
+          <t>2026-10-23 12:37:49</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E22" s="10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F22" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:28</t>
+          <t>2026-10-23 12:36:31</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E23" s="10" t="n">
@@ -1098,7 +1098,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:36:26</t>
+          <t>2026-10-23 12:36:30</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E24" s="10" t="n">
@@ -1134,7 +1134,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:18</t>
+          <t>2026-10-23 12:36:28</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -1153,24 +1153,24 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F25" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:16</t>
+          <t>2026-10-23 12:36:26</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F26" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:34:14</t>
+          <t>2026-10-23 12:34:18</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F27" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:32:15</t>
+          <t>2026-10-23 12:34:16</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E28" s="10" t="n">
@@ -1271,14 +1271,14 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:32:13</t>
+          <t>2026-10-23 12:34:14</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1293,28 +1293,28 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E29" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F29" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:18:37</t>
+          <t>2026-10-23 12:32:15</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1324,22 +1324,22 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:14:37</t>
+          <t>2026-10-23 12:32:13</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1360,33 +1360,33 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:06:56</t>
+          <t>2026-10-23 12:18:37</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="E32" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F32" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:06:55</t>
+          <t>2026-10-23 12:14:37</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E33" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:16</t>
+          <t>2026-10-23 12:06:56</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E34" s="10" t="n">
@@ -1494,7 +1494,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:15</t>
+          <t>2026-10-23 12:06:55</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1504,22 +1504,22 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F35" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 12:01:13</t>
+          <t>2026-10-23 12:01:16</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1566,7 +1566,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:55:01</t>
+          <t>2026-10-23 12:01:15</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E37" s="10" t="n">
@@ -1602,7 +1602,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:41</t>
+          <t>2026-10-23 12:01:13</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F38" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:26</t>
+          <t>2026-10-23 11:55:01</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1674,7 +1674,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:24</t>
+          <t>2026-10-23 11:54:41</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:54:23</t>
+          <t>2026-10-23 11:54:26</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F41" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 11:18:39</t>
+          <t>2026-10-23 11:54:24</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E42" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:54:31</t>
+          <t>2026-10-23 11:54:23</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1792,22 +1792,22 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E43" s="10" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F43" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:53:48</t>
+          <t>2026-10-23 11:18:39</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E44" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F44" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:28</t>
+          <t>2026-10-23 10:54:31</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>96.67</v>
+        <v>99</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>26.67</v>
+        <v>49</v>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:27</t>
+          <t>2026-10-23 10:53:48</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>96.67</v>
+        <v>99</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>26.67</v>
+        <v>49</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:48:25</t>
+          <t>2026-10-23 10:48:28</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -1962,7 +1962,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:42:29</t>
+          <t>2026-10-23 10:48:27</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -1972,22 +1972,22 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E48" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>99</v>
+        <v>96.67</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>44</v>
+        <v>26.67</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:42:15</t>
+          <t>2026-10-23 10:48:25</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -2008,33 +2008,33 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E49" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>99</v>
+        <v>96.67</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>44</v>
+        <v>26.67</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:50</t>
+          <t>2026-10-23 10:42:29</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:49</t>
+          <t>2026-10-23 10:42:15</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -2099,14 +2099,14 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:47</t>
+          <t>2026-10-23 10:38:50</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -2142,7 +2142,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:46</t>
+          <t>2026-10-23 10:38:49</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -2178,7 +2178,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:38:44</t>
+          <t>2026-10-23 10:38:47</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:31:15</t>
+          <t>2026-10-23 10:38:46</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="E55" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F55" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 10:20:19</t>
+          <t>2026-10-23 10:38:44</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -2260,22 +2260,22 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F56" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:07:43</t>
+          <t>2026-10-23 10:31:15</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:07:42</t>
+          <t>2026-10-23 10:20:19</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -2332,22 +2332,22 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:51</t>
+          <t>2026-10-23 09:07:43</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:49</t>
+          <t>2026-10-23 09:07:42</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -2404,22 +2404,22 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:50:47</t>
+          <t>2026-10-23 08:50:51</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E61" s="10" t="n">
@@ -2466,7 +2466,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:31:27</t>
+          <t>2026-10-23 08:50:49</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E62" s="10" t="n">
@@ -2502,7 +2502,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 08:31:23</t>
+          <t>2026-10-23 08:50:47</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F63" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 07:41:41</t>
+          <t>2026-10-23 08:31:27</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
@@ -2557,24 +2557,24 @@
         </is>
       </c>
       <c r="E64" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F64" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 07:41:40</t>
+          <t>2026-10-23 08:31:23</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E65" s="10" t="n">
@@ -2603,14 +2603,14 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 06:41:44</t>
+          <t>2026-10-23 07:41:41</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -2620,33 +2620,33 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 06:30:39</t>
+          <t>2026-10-23 07:41:40</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -2656,33 +2656,33 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E67" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F67" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 05:19:16</t>
+          <t>2026-10-23 06:41:44</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E68" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G68" s="10" t="n">
         <v>65</v>
-      </c>
-      <c r="F68" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G68" s="10" t="n">
-        <v>34</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 05:19:15</t>
+          <t>2026-10-23 06:30:39</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:41:25</t>
+          <t>2026-10-23 05:19:16</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F70" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:41:24</t>
+          <t>2026-10-23 05:19:15</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="E71" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F71" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 04:24:21</t>
+          <t>2026-10-23 04:41:25</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -2862,7 +2862,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:02:01</t>
+          <t>2026-10-23 04:41:24</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -2872,22 +2872,22 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E73" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F73" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 03:02:00</t>
+          <t>2026-10-23 04:24:21</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E74" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F74" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 16:36:34</t>
+          <t>2026-10-23 03:02:01</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -2953,24 +2953,24 @@
         </is>
       </c>
       <c r="E75" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F75" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:42:05</t>
+          <t>2026-10-23 03:02:00</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:42:04</t>
+          <t>2026-10-22 16:36:34</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
@@ -3025,24 +3025,24 @@
         </is>
       </c>
       <c r="E77" s="10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:41:30</t>
+          <t>2026-10-22 14:42:05</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -3061,24 +3061,24 @@
         </is>
       </c>
       <c r="E78" s="10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:11:48</t>
+          <t>2026-10-22 14:42:04</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -3088,33 +3088,33 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E79" s="10" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="F79" s="10" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:11:47</t>
+          <t>2026-10-22 14:41:30</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -3124,22 +3124,22 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E80" s="10" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:10:30</t>
+          <t>2026-10-22 14:11:48</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -3160,22 +3160,22 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E81" s="10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F81" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:53:02</t>
+          <t>2026-10-22 14:11:47</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -3196,33 +3196,33 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E82" s="10" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:48</t>
+          <t>2026-10-22 14:10:30</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E83" s="10" t="n">
         <v>60</v>
       </c>
       <c r="F83" s="10" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="G83" s="10" t="n">
-        <v>38.33</v>
+        <v>39</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:46</t>
+          <t>2026-10-22 13:53:02</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -3273,28 +3273,28 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E84" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>38.33</v>
+        <v>44</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:45</t>
+          <t>2026-10-22 13:44:48</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3330,7 +3330,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:38</t>
+          <t>2026-10-22 13:44:46</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:37</t>
+          <t>2026-10-22 13:44:45</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3402,7 +3402,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:44:35</t>
+          <t>2026-10-22 13:44:38</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:36:21</t>
+          <t>2026-10-22 13:44:37</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -3448,33 +3448,33 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E89" s="10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>97</v>
+        <v>98.33</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>62</v>
+        <v>38.33</v>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:36:19</t>
+          <t>2026-10-22 13:44:35</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -3489,28 +3489,28 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E90" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>97</v>
+        <v>98.33</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>42</v>
+        <v>38.33</v>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:22:36</t>
+          <t>2026-10-22 13:36:21</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -3520,22 +3520,22 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:12:21</t>
+          <t>2026-10-22 13:36:19</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E92" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:12:00</t>
+          <t>2026-10-22 13:22:36</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 13:06:29</t>
+          <t>2026-10-22 13:12:21</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
@@ -3637,13 +3637,13 @@
         </is>
       </c>
       <c r="E94" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:38:17</t>
+          <t>2026-10-22 13:12:00</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
@@ -3673,24 +3673,24 @@
         </is>
       </c>
       <c r="E95" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F95" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:41</t>
+          <t>2026-10-22 13:06:29</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="E96" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F96" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:39</t>
+          <t>2026-10-22 12:38:17</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -3736,22 +3736,22 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E97" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F97" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:38</t>
+          <t>2026-10-22 12:17:41</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -3777,17 +3777,17 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E98" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F98" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:17:36</t>
+          <t>2026-10-22 12:17:39</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E99" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F99" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:18</t>
+          <t>2026-10-22 12:17:38</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -3844,22 +3844,22 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E100" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:01</t>
+          <t>2026-10-22 12:17:36</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E101" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F101" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:02:00</t>
+          <t>2026-10-22 12:02:18</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -3916,22 +3916,22 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E102" s="10" t="n">
         <v>70</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 12:01:58</t>
+          <t>2026-10-22 12:02:01</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -3978,7 +3978,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:21</t>
+          <t>2026-10-22 12:02:00</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -3993,17 +3993,17 @@
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E104" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F104" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:19</t>
+          <t>2026-10-22 12:01:58</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E105" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F105" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:38:18</t>
+          <t>2026-10-22 11:38:21</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -4086,7 +4086,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:10:19</t>
+          <t>2026-10-22 11:38:19</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E107" s="10" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F107" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G107" s="10" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:58</t>
+          <t>2026-10-22 11:38:18</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -4158,7 +4158,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:57</t>
+          <t>2026-10-22 11:10:19</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -4168,22 +4168,22 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E109" s="10" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="F109" s="10" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G109" s="10" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:33:55</t>
+          <t>2026-10-22 10:33:58</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -4204,22 +4204,22 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E110" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F110" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G110" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 10:20:38</t>
+          <t>2026-10-22 10:33:57</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E111" s="10" t="n">
@@ -4266,7 +4266,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:42:30</t>
+          <t>2026-10-22 10:33:55</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E112" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F112" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:42:28</t>
+          <t>2026-10-22 10:20:38</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
@@ -4321,13 +4321,13 @@
         </is>
       </c>
       <c r="E113" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F113" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G113" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:35:08</t>
+          <t>2026-10-22 09:42:30</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -4348,33 +4348,33 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E114" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:35:07</t>
+          <t>2026-10-22 09:42:28</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -4389,28 +4389,28 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E115" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F115" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:51</t>
+          <t>2026-10-22 09:35:08</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -4420,33 +4420,33 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E116" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:13:38</t>
+          <t>2026-10-22 09:35:07</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -4456,33 +4456,33 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E117" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F117" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 07:04:15</t>
+          <t>2026-10-22 09:22:51</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 07:04:13</t>
+          <t>2026-10-22 09:13:38</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
@@ -4537,24 +4537,24 @@
         </is>
       </c>
       <c r="E119" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F119" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:11:41</t>
+          <t>2026-10-22 07:04:15</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -4564,22 +4564,22 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E120" s="10" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G120" s="10" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:11:40</t>
+          <t>2026-10-22 07:04:13</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -4600,22 +4600,22 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E121" s="10" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F121" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:05:31</t>
+          <t>2026-10-22 06:11:41</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -4636,33 +4636,33 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E122" s="10" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G122" s="10" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 06:05:30</t>
+          <t>2026-10-22 06:11:40</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -4672,33 +4672,33 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E123" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="F123" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G123" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="F123" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G123" s="10" t="n">
-        <v>39</v>
-      </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:28</t>
+          <t>2026-10-22 06:05:31</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -4708,33 +4708,33 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E124" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F124" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G124" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:26</t>
+          <t>2026-10-22 06:05:30</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:24</t>
+          <t>2026-10-22 03:58:28</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -4780,22 +4780,22 @@
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E126" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F126" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G126" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:23</t>
+          <t>2026-10-22 03:58:26</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="E127" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F127" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G127" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:21</t>
+          <t>2026-10-22 03:58:24</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="E128" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F128" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G128" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:58:20</t>
+          <t>2026-10-22 03:58:23</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E129" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F129" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G129" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:43:08</t>
+          <t>2026-10-22 03:58:21</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:14:27</t>
+          <t>2026-10-22 03:58:20</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E131" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F131" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G131" s="10" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 03:14:26</t>
+          <t>2026-10-22 03:43:08</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E132" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F132" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G132" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 02:59:11</t>
+          <t>2026-10-22 03:14:27</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -5032,22 +5032,22 @@
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E133" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F133" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G133" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:57:03</t>
+          <t>2026-10-22 03:14:26</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -5068,22 +5068,22 @@
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E134" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G134" s="10" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:09:58</t>
+          <t>2026-10-22 02:59:11</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E135" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F135" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G135" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:09:57</t>
+          <t>2026-10-21 14:57:03</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -5140,22 +5140,22 @@
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E136" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G136" s="10" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:21</t>
+          <t>2026-10-21 14:09:58</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -5181,17 +5181,17 @@
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E137" s="10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F137" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G137" s="10" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:20</t>
+          <t>2026-10-21 14:09:57</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -5212,22 +5212,22 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E138" s="10" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F138" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G138" s="10" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:18</t>
+          <t>2026-10-21 13:43:21</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="E139" s="10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F139" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:43:17</t>
+          <t>2026-10-21 13:43:20</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
@@ -5293,13 +5293,13 @@
         </is>
       </c>
       <c r="E140" s="10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F140" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G140" s="10" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:38</t>
+          <t>2026-10-21 13:43:18</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:42:22</t>
+          <t>2026-10-21 13:43:17</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -5375,14 +5375,14 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:33:00</t>
+          <t>2026-10-21 13:42:38</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -5392,22 +5392,22 @@
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E143" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F143" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:32:58</t>
+          <t>2026-10-21 13:42:22</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -5433,28 +5433,28 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E144" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F144" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G144" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:35</t>
+          <t>2026-10-21 13:33:00</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="C145" s="9" t="inlineStr">
         <is>
-          <t>เสื้อฟอก</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>3XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E145" s="10" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>153.33</v>
+        <v>99</v>
       </c>
       <c r="G145" s="10" t="n">
-        <v>38.33</v>
+        <v>49</v>
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:34</t>
+          <t>2026-10-21 13:32:58</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -5500,22 +5500,22 @@
       </c>
       <c r="C146" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E146" s="10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>93.33</v>
+        <v>99</v>
       </c>
       <c r="G146" s="10" t="n">
-        <v>58.33</v>
+        <v>39</v>
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:42:32</t>
+          <t>2026-10-21 12:42:35</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="C147" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อฟอก</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>3XL</t>
         </is>
       </c>
       <c r="E147" s="10" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="F147" s="10" t="n">
-        <v>93.33</v>
+        <v>153.33</v>
       </c>
       <c r="G147" s="10" t="n">
         <v>38.33</v>
@@ -5562,7 +5562,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:40:53</t>
+          <t>2026-10-21 12:42:34</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="C148" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E148" s="10" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>99</v>
+        <v>93.33</v>
       </c>
       <c r="G148" s="10" t="n">
-        <v>49</v>
+        <v>58.33</v>
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:40:51</t>
+          <t>2026-10-21 12:42:32</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -5613,17 +5613,17 @@
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E149" s="10" t="n">
         <v>55</v>
       </c>
       <c r="F149" s="10" t="n">
-        <v>99</v>
+        <v>93.33</v>
       </c>
       <c r="G149" s="10" t="n">
-        <v>44</v>
+        <v>38.33</v>
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:12:24</t>
+          <t>2026-10-21 12:40:53</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C150" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
@@ -5653,13 +5653,13 @@
         </is>
       </c>
       <c r="E150" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G150" s="10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:04:00</t>
+          <t>2026-10-21 12:40:51</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -5685,28 +5685,28 @@
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E151" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F151" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G151" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:53</t>
+          <t>2026-10-21 11:12:24</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E152" s="10" t="n">
@@ -5742,7 +5742,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:51</t>
+          <t>2026-10-21 11:04:00</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -5752,33 +5752,33 @@
       </c>
       <c r="C153" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E153" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F153" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G153" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:28:25</t>
+          <t>2026-10-21 10:28:53</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -5788,33 +5788,33 @@
       </c>
       <c r="C154" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E154" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F154" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G154" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:18:07</t>
+          <t>2026-10-21 10:28:51</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -5829,17 +5829,17 @@
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E155" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F155" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G155" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:03:38</t>
+          <t>2026-10-21 10:28:25</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -5860,33 +5860,33 @@
       </c>
       <c r="C156" s="9" t="inlineStr">
         <is>
-          <t>กางเกง</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E156" s="10" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F156" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G156" s="10" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 08:42:43</t>
+          <t>2026-10-21 10:18:07</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="C157" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
@@ -5905,24 +5905,24 @@
         </is>
       </c>
       <c r="E157" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F157" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G157" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 06:06:13</t>
+          <t>2026-10-21 10:03:38</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="C158" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E158" s="10" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F158" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G158" s="10" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:21</t>
+          <t>2026-10-21 08:42:43</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -5987,14 +5987,14 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:20</t>
+          <t>2026-10-21 06:06:13</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -6009,17 +6009,17 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E160" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F160" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G160" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:18</t>
+          <t>2026-10-21 05:58:21</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -6066,7 +6066,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:17</t>
+          <t>2026-10-21 05:58:20</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:15</t>
+          <t>2026-10-21 05:58:18</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E163" s="10" t="n">
@@ -6138,7 +6138,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:58:14</t>
+          <t>2026-10-21 05:58:17</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E164" s="10" t="n">
@@ -6174,7 +6174,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:12:11</t>
+          <t>2026-10-21 05:58:15</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E165" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F165" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G165" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:12:09</t>
+          <t>2026-10-21 05:58:14</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E166" s="10" t="n">
@@ -6246,7 +6246,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 05:05:15</t>
+          <t>2026-10-21 05:12:11</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E167" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F167" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G167" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 04:29:02</t>
+          <t>2026-10-21 05:12:09</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E168" s="10" t="n">
@@ -6318,7 +6318,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 04:02:39</t>
+          <t>2026-10-21 05:05:15</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E169" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F169" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G169" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:55:22</t>
+          <t>2026-10-21 04:29:02</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -6390,7 +6390,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:55:20</t>
+          <t>2026-10-21 04:02:39</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E171" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F171" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G171" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:26:16</t>
+          <t>2026-10-20 14:55:22</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E172" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F172" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G172" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:11:00</t>
+          <t>2026-10-20 14:55:20</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 14:10:58</t>
+          <t>2026-10-20 14:26:16</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -6513,17 +6513,17 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E174" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F174" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G174" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:47:43</t>
+          <t>2026-10-20 14:11:00</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -6544,22 +6544,22 @@
       </c>
       <c r="C175" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E175" s="10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F175" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G175" s="10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:42:10</t>
+          <t>2026-10-20 14:10:58</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="C176" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E176" s="10" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G176" s="10" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:42:08</t>
+          <t>2026-10-20 13:47:43</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="C177" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
@@ -6625,13 +6625,13 @@
         </is>
       </c>
       <c r="E177" s="10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F177" s="10" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="G177" s="10" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:32</t>
+          <t>2026-10-20 13:42:10</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
@@ -6661,13 +6661,13 @@
         </is>
       </c>
       <c r="E178" s="10" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G178" s="10" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:30</t>
+          <t>2026-10-20 13:42:08</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -6688,22 +6688,22 @@
       </c>
       <c r="C179" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E179" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F179" s="10" t="n">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="G179" s="10" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:27:29</t>
+          <t>2026-10-20 13:27:32</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -6729,17 +6729,17 @@
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E180" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F180" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G180" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:15:35</t>
+          <t>2026-10-20 13:27:30</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -6760,22 +6760,22 @@
       </c>
       <c r="C181" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E181" s="10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F181" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G181" s="10" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 13:03:38</t>
+          <t>2026-10-20 13:27:29</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -6822,7 +6822,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 12:06:30</t>
+          <t>2026-10-20 13:15:35</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -6832,22 +6832,22 @@
       </c>
       <c r="C183" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E183" s="10" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F183" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G183" s="10" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 12:06:28</t>
+          <t>2026-10-20 13:03:38</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -6868,22 +6868,22 @@
       </c>
       <c r="C184" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E184" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F184" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G184" s="10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:53:57</t>
+          <t>2026-10-20 12:06:30</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E185" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F185" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G185" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:18:17</t>
+          <t>2026-10-20 12:06:28</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -6940,33 +6940,33 @@
       </c>
       <c r="C186" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬาแขนยาว</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E186" s="10" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G186" s="10" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:18:15</t>
+          <t>2026-10-20 11:53:57</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -6976,33 +6976,33 @@
       </c>
       <c r="C187" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืดแขนยาว</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E187" s="10" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F187" s="10" t="n">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G187" s="10" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>คนละครึ่ง</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:54:57</t>
+          <t>2026-10-20 11:18:17</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -7012,33 +7012,33 @@
       </c>
       <c r="C188" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อกีฬาแขนยาว</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E188" s="10" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F188" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G188" s="10" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:54:56</t>
+          <t>2026-10-20 11:18:15</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -7048,33 +7048,33 @@
       </c>
       <c r="C189" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืดแขนยาว</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E189" s="10" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F189" s="10" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="G189" s="10" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>คนละครึ่ง</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:33:40</t>
+          <t>2026-10-20 10:54:57</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -7110,7 +7110,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:15:31</t>
+          <t>2026-10-20 10:54:56</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="C191" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
@@ -7129,13 +7129,13 @@
         </is>
       </c>
       <c r="E191" s="10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F191" s="10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G191" s="10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:15:29</t>
+          <t>2026-10-20 10:33:40</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="C192" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="E192" s="10" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F192" s="10" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G192" s="10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 10:08:11</t>
+          <t>2026-10-20 10:15:31</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -7192,33 +7192,33 @@
       </c>
       <c r="C193" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E193" s="10" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F193" s="10" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G193" s="10" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 09:29:03</t>
+          <t>2026-10-20 10:15:29</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -7228,22 +7228,22 @@
       </c>
       <c r="C194" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E194" s="10" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="F194" s="10" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G194" s="10" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:24:03</t>
+          <t>2026-10-20 10:08:11</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -7269,28 +7269,28 @@
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E195" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F195" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G195" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:24:02</t>
+          <t>2026-10-20 09:29:03</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="C196" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E196" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F196" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G196" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 08:15:42</t>
+          <t>2026-10-20 08:24:03</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E197" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F197" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G197" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:33</t>
+          <t>2026-10-20 08:24:02</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -7377,17 +7377,17 @@
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E198" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F198" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G198" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:31</t>
+          <t>2026-10-20 08:15:42</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E199" s="10" t="n">
@@ -7434,7 +7434,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:29</t>
+          <t>2026-10-20 07:33:33</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -7449,17 +7449,17 @@
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E200" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F200" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G200" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 07:33:28</t>
+          <t>2026-10-20 07:33:31</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -7485,17 +7485,17 @@
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>2XL</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E201" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F201" s="10" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G201" s="10" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 06:01:14</t>
+          <t>2026-10-20 07:33:29</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -7516,22 +7516,22 @@
       </c>
       <c r="C202" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E202" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F202" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G202" s="10" t="n">
         <v>50</v>
-      </c>
-      <c r="F202" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G202" s="10" t="n">
-        <v>49</v>
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:59:54</t>
+          <t>2026-10-20 07:33:28</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -7552,33 +7552,33 @@
       </c>
       <c r="C203" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>2XL</t>
         </is>
       </c>
       <c r="E203" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F203" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G203" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="F203" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="G203" s="10" t="n">
-        <v>49</v>
-      </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:59:52</t>
+          <t>2026-10-20 06:01:14</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -7588,33 +7588,33 @@
       </c>
       <c r="C204" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E204" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F204" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G204" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>โอนเงิน</t>
+          <t>เงินสด</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:03</t>
+          <t>2026-10-20 05:59:54</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -7629,17 +7629,17 @@
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E205" s="10" t="n">
         <v>50</v>
       </c>
       <c r="F205" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G205" s="10" t="n">
-        <v>48.75</v>
+        <v>49</v>
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:02</t>
+          <t>2026-10-20 05:59:52</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -7660,22 +7660,22 @@
       </c>
       <c r="C206" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E206" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F206" s="10" t="n">
-        <v>98.75</v>
+        <v>99</v>
       </c>
       <c r="G206" s="10" t="n">
-        <v>48.75</v>
+        <v>39</v>
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:43:00</t>
+          <t>2026-10-20 05:43:03</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -7696,22 +7696,22 @@
       </c>
       <c r="C207" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E207" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F207" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G207" s="10" t="n">
-        <v>38.75</v>
+        <v>48.75</v>
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:58</t>
+          <t>2026-10-20 05:43:02</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -7732,22 +7732,22 @@
       </c>
       <c r="C208" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E208" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F208" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G208" s="10" t="n">
-        <v>43.75</v>
+        <v>48.75</v>
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
@@ -7758,7 +7758,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:57</t>
+          <t>2026-10-20 05:43:00</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C209" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E209" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F209" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G209" s="10" t="n">
-        <v>43.75</v>
+        <v>38.75</v>
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:55</t>
+          <t>2026-10-20 05:42:58</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -7809,17 +7809,17 @@
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E210" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F210" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G210" s="10" t="n">
-        <v>38.75</v>
+        <v>43.75</v>
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:54</t>
+          <t>2026-10-20 05:42:57</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -7845,17 +7845,17 @@
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E211" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F211" s="10" t="n">
         <v>98.75</v>
       </c>
       <c r="G211" s="10" t="n">
-        <v>38.75</v>
+        <v>43.75</v>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:42:52</t>
+          <t>2026-10-20 05:42:55</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -7902,7 +7902,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:20:48</t>
+          <t>2026-10-20 05:42:54</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -7912,33 +7912,33 @@
       </c>
       <c r="C213" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E213" s="10" t="n">
         <v>60</v>
       </c>
       <c r="F213" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G213" s="10" t="n">
-        <v>39</v>
+        <v>38.75</v>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 05:01:04</t>
+          <t>2026-10-20 05:42:52</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E214" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F214" s="10" t="n">
-        <v>99</v>
+        <v>98.75</v>
       </c>
       <c r="G214" s="10" t="n">
-        <v>44</v>
+        <v>38.75</v>
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 04:20:18</t>
+          <t>2026-10-20 05:20:48</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -7989,17 +7989,17 @@
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E215" s="10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F215" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G215" s="10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 04:20:17</t>
+          <t>2026-10-20 05:01:04</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -8020,33 +8020,33 @@
       </c>
       <c r="C216" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E216" s="10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F216" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G216" s="10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
-          <t>เงินสด</t>
+          <t>โอนเงิน</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-10-20 03:58:57</t>
+          <t>2026-10-20 04:20:18</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C217" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
@@ -8065,13 +8065,13 @@
         </is>
       </c>
       <c r="E217" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F217" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G217" s="10" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:42</t>
+          <t>2026-10-20 04:20:17</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -8092,22 +8092,22 @@
       </c>
       <c r="C218" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E218" s="10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F218" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G218" s="10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:40</t>
+          <t>2026-10-20 03:58:57</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -8133,17 +8133,17 @@
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E219" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F219" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G219" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:19:39</t>
+          <t>2026-10-19 13:19:42</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="C220" s="9" t="inlineStr">
         <is>
-          <t>เสื้อยืด</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
@@ -8190,7 +8190,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:46</t>
+          <t>2026-10-19 13:19:40</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -8200,22 +8200,22 @@
       </c>
       <c r="C221" s="9" t="inlineStr">
         <is>
-          <t>กางเกง FT</t>
+          <t>เสื้อกีฬา</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E221" s="10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F221" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G221" s="10" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:45</t>
+          <t>2026-10-19 13:19:39</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -8236,22 +8236,22 @@
       </c>
       <c r="C222" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>เสื้อยืด</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E222" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F222" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G222" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H222" s="9" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:13:44</t>
+          <t>2026-10-19 13:13:46</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -8272,22 +8272,22 @@
       </c>
       <c r="C223" s="9" t="inlineStr">
         <is>
-          <t>เสื้อกีฬา</t>
+          <t>กางเกง FT</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E223" s="10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G223" s="10" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:16:37</t>
+          <t>2026-10-19 13:13:45</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E224" s="10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F224" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G224" s="10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:14:20</t>
+          <t>2026-10-19 13:13:44</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -8370,7 +8370,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:28</t>
+          <t>2026-10-19 11:16:37</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -8385,17 +8385,17 @@
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E226" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F226" s="10" t="n">
         <v>99</v>
       </c>
       <c r="G226" s="10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:26</t>
+          <t>2026-10-19 11:14:20</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -8442,7 +8442,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 10:14:24</t>
+          <t>2026-10-19 10:14:28</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="E228" s="10" t="n">
@@ -8470,6 +8470,78 @@
         <v>39</v>
       </c>
       <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:26</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E229" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F229" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G229" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H229" s="9" t="inlineStr">
+        <is>
+          <t>เงินสด</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 10:14:24</t>
+        </is>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>งานแข่งเรือหล่มเก่า2569</t>
+        </is>
+      </c>
+      <c r="C230" s="9" t="inlineStr">
+        <is>
+          <t>เสื้อกีฬา</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E230" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F230" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="G230" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
         <is>
           <t>เงินสด</t>
         </is>
